--- a/final 4.xlsx
+++ b/final 4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29523"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jatin.x.Agarwal\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aditya.chauhan2\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84DFA432-3845-4458-8D1D-DF8652498109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{167A6780-C074-48F2-84CA-AB963FC7A9CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3000" yWindow="3000" windowWidth="15120" windowHeight="8664" xr2:uid="{C8A15387-D69A-47CB-A4CA-1EDA47A256CD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{C8A15387-D69A-47CB-A4CA-1EDA47A256CD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,9 +41,6 @@
     <t>IGA Code</t>
   </si>
   <si>
-    <t xml:space="preserve"> Name</t>
-  </si>
-  <si>
     <t xml:space="preserve"> From Date </t>
   </si>
   <si>
@@ -84,13 +81,16 @@
   </si>
   <si>
     <t>16/06/2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Employee Name</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -463,84 +463,84 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D92DDC2-C440-4E55-98E6-336F04A53606}">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.7109375" customWidth="1"/>
     <col min="4" max="4" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>56499</v>
       </c>
       <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>31454</v>
       </c>
       <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>32743</v>
       </c>
       <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>11</v>
       </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>38721</v>
       </c>
       <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
         <v>13</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>14</v>
       </c>
-      <c r="D5" t="s">
-        <v>15</v>
-      </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C6" s="1"/>
     </row>
   </sheetData>
